--- a/appointment_forms/036_financial_review_appointment_form_template--appointment_forms.xlsx
+++ b/appointment_forms/036_financial_review_appointment_form_template--appointment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>contact_information</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -548,30 +548,30 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>appointment_details</t>
+          <t>Appointment Details</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,41 +589,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>purpose</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Purpose</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>purpose_of_appointment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>Purpose of Appointment</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>contact_person</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Contact Person</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,23 +653,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>appointment_type</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>Appointment Type</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,16 +681,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>additional_comments</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Additional Comments</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -707,12 +730,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -735,153 +758,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>services_choices</t>
+          <t>appointment_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>investment_advice</t>
+          <t>self</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Investment Advice</t>
+          <t>Self</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>services_choices</t>
+          <t>appointment_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>insurance_planning</t>
+          <t>someone_else</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Insurance Planning</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>services_choices</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>retirement_planning</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Retirement Planning</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>services_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>investment_advice</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Investment Advice</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>services_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>insurance_planning</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Insurance Planning</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>services_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>retirement_planning</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Retirement Planning</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>services_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>investment_advice</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Investment Advice</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>services_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>insurance_planning</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Insurance Planning</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>services_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>retirement_planning</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Retirement Planning</t>
+          <t>Someone Else</t>
         </is>
       </c>
     </row>
